--- a/results/full_birds_summary/birds_BinaryVector_summary.xlsx
+++ b/results/full_birds_summary/birds_BinaryVector_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE12"/>
+  <dimension ref="A1:BE14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3869,6 +3869,580 @@
       <c r="BE12" t="inlineStr">
         <is>
           <t>0.3860±0.0366</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ecc</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0.8684±0.0395</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0.8373±0.0495</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.7960±0.0587</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.6945±0.0640</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.6245±0.0242</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.6170±0.0206</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.5719±0.0369</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.3687±0.0424</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.5570±0.0152</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0.5563±0.0163</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.5266±0.0289</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0.3825±0.0385</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.5756±0.0131</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.5723±0.0149</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0.5357±0.0294</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>0.3600±0.0376</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>0.9563±0.0043</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0.9548±0.0048</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>0.9465±0.0056</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>0.9046±0.0089</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0.5556±0.0162</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0.5509±0.0166</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0.5110±0.0273</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>0.3283±0.0360</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>0.1528±0.0221</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>0.1871±0.0399</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>0.1975±0.0542</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>0.1777±0.0382</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>0.3184±0.0560</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>0.3621±0.0745</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>0.2966±0.0745</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>0.1734±0.0399</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>0.1087±0.0179</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>0.1368±0.0313</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>0.1685±0.0547</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>0.2271±0.0569</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>0.9827±0.0092</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>0.3333±0.0434</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>0.3514±0.0551</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>0.3329±0.0705</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>0.2521±0.0392</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>0.8674±0.0342</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>0.7375±0.0758</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>0.4859±0.0745</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>0.2169±0.0367</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>0.2069±0.0310</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>0.2324±0.0440</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>0.2555±0.0641</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>0.3030±0.0464</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>0.5008±0.0280</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>0.4921±0.0281</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0.4465±0.0340</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0.2540±0.0360</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>mlknn</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0.9589±0.0379</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.9212±0.0396</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.8778±0.0376</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0.7210±0.0500</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0.4876±0.0327</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.4863±0.0451</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.3740±0.0490</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.1316±0.0387</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.4742±0.0361</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0.4690±0.0473</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0.3632±0.0508</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>0.1643±0.0428</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0.4777±0.0350</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0.4723±0.0455</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0.3619±0.0501</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0.1369±0.0396</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>0.9450±0.0075</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0.9394±0.0080</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>0.9195±0.0115</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>0.8472±0.0169</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0.4739±0.0362</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0.4638±0.0458</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>0.3490±0.0514</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>0.1145±0.0385</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>0.0215±0.0138</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>0.0541±0.0264</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>0.0651±0.0182</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>0.0827±0.0185</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>0.0364±0.0205</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>0.0916±0.0434</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>0.0920±0.0382</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>0.0729±0.0212</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>0.0160±0.0110</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>0.0463±0.0298</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>0.0680±0.0209</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>0.1519±0.0331</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>0.9911±0.0103</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>0.0620±0.0394</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>0.1065±0.0347</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>0.1158±0.0324</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>0.1124±0.0203</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>0.2874±0.1448</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>0.2624±0.0728</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>0.1418±0.0379</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>0.0822±0.0174</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>0.0353±0.0233</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>0.0696±0.0274</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>0.1000±0.0329</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>0.1827±0.0373</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>0.4651±0.0395</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>0.4437±0.0475</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.3209±0.0543</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.0710±0.0374</t>
         </is>
       </c>
     </row>
